--- a/ILLIA/Mayo/ILLIA-MAYO.xlsx
+++ b/ILLIA/Mayo/ILLIA-MAYO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EF988D-C75F-4457-A279-CF9922AAB6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9ED015-2164-43C3-8F4E-532732E22653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -517,9 +517,6 @@
     <t>MANTENIMIENTO DE CUENTA BANCARIA</t>
   </si>
   <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
     <t>Seguro Sra. Cristina</t>
   </si>
   <si>
@@ -593,6 +590,9 @@
   </si>
   <si>
     <t>LAS EXPENSAS SON CERRADAS EL DIA 29/05 A LAS 12 DEL MEDIODIA ENTENDIENDO QUE UNA GRAN PARTE DE LOS VECINOS NO ABONO LAS EXPENSAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debito </t>
   </si>
 </sst>
 </file>
@@ -1895,21 +1895,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="14" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1940,37 +1937,36 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1982,15 +1978,19 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="14" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2291,11 +2291,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="226" t="s">
+      <c r="B3" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="226"/>
-      <c r="D3" s="226"/>
+      <c r="C3" s="225"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="9"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -2303,9 +2303,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
-      <c r="B4" s="227"/>
-      <c r="C4" s="227"/>
-      <c r="D4" s="227"/>
+      <c r="B4" s="226"/>
+      <c r="C4" s="226"/>
+      <c r="D4" s="226"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -2330,7 +2330,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15" t="s">
@@ -2343,13 +2343,13 @@
       <c r="I6" s="156"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="236" t="s">
+      <c r="A7" s="235" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="237"/>
-      <c r="C7" s="237"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="238"/>
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="237"/>
       <c r="F7" s="17"/>
       <c r="G7" s="157"/>
       <c r="H7" s="157"/>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="239" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="221"/>
+      <c r="B9" s="238" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="239"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -2384,8 +2384,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="222"/>
-      <c r="C11" s="224"/>
+      <c r="B11" s="242"/>
+      <c r="C11" s="243"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -2403,22 +2403,22 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="242" t="s">
+      <c r="A14" s="244" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="220"/>
-      <c r="C14" s="220"/>
-      <c r="D14" s="220"/>
-      <c r="E14" s="221"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="239"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="240"/>
-      <c r="B15" s="243"/>
-      <c r="C15" s="243"/>
-      <c r="D15" s="243"/>
+      <c r="B15" s="246"/>
+      <c r="C15" s="246"/>
+      <c r="D15" s="246"/>
       <c r="E15" s="241"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2426,20 +2426,20 @@
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="240"/>
-      <c r="B16" s="243"/>
-      <c r="C16" s="243"/>
-      <c r="D16" s="243"/>
+      <c r="B16" s="246"/>
+      <c r="C16" s="246"/>
+      <c r="D16" s="246"/>
       <c r="E16" s="241"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="222"/>
-      <c r="B17" s="223"/>
-      <c r="C17" s="223"/>
-      <c r="D17" s="223"/>
-      <c r="E17" s="224"/>
+      <c r="A17" s="242"/>
+      <c r="B17" s="247"/>
+      <c r="C17" s="247"/>
+      <c r="D17" s="247"/>
+      <c r="E17" s="243"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="29" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="34" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="35" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -2852,10 +2852,10 @@
         <v>121</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C40" s="25"/>
-      <c r="D40" s="260">
+      <c r="D40" s="217">
         <v>28000</v>
       </c>
       <c r="E40" s="34"/>
@@ -2886,7 +2886,7 @@
         <v>13</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C41" s="25"/>
       <c r="D41" s="190">
@@ -2897,7 +2897,7 @@
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -2962,16 +2962,16 @@
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="244" t="s">
+      <c r="A44" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="218"/>
+      <c r="B44" s="224"/>
       <c r="C44" s="37"/>
       <c r="D44" s="199">
         <v>50274.73</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F44" s="4"/>
     </row>
@@ -3032,17 +3032,17 @@
       </c>
       <c r="B48" s="25"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="262">
+      <c r="D48" s="219">
         <v>335906.93</v>
       </c>
       <c r="E48" s="165" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B49" s="25" t="s">
         <v>18</v>
@@ -3052,7 +3052,7 @@
         <v>25738.5</v>
       </c>
       <c r="E49" s="46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -3105,7 +3105,7 @@
         <v>20</v>
       </c>
       <c r="C51" s="160"/>
-      <c r="D51" s="263">
+      <c r="D51" s="220">
         <v>2859.83</v>
       </c>
       <c r="E51" s="47" t="str">
@@ -3162,16 +3162,16 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="229" t="s">
-        <v>168</v>
-      </c>
-      <c r="B54" s="218"/>
+      <c r="A54" s="228" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" s="224"/>
       <c r="C54" s="25"/>
       <c r="D54" s="203">
         <v>94000</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -3205,7 +3205,7 @@
         <v>30000</v>
       </c>
       <c r="E55" s="163" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -3235,21 +3235,21 @@
       </c>
       <c r="B56" s="138"/>
       <c r="C56" s="49"/>
-      <c r="D56" s="264">
+      <c r="D56" s="221">
         <v>18763.05</v>
       </c>
       <c r="E56" s="163" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="F56" s="50"/>
       <c r="G56" s="50"/>
       <c r="H56" s="50"/>
     </row>
     <row r="57" spans="1:26" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="217" t="s">
-        <v>178</v>
-      </c>
-      <c r="B57" s="218"/>
+      <c r="A57" s="223" t="s">
+        <v>177</v>
+      </c>
+      <c r="B57" s="224"/>
       <c r="C57" s="49"/>
       <c r="D57" s="204"/>
       <c r="E57" s="150"/>
@@ -3258,32 +3258,32 @@
       <c r="H57" s="50"/>
     </row>
     <row r="58" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="217" t="s">
-        <v>169</v>
-      </c>
-      <c r="B58" s="218"/>
+      <c r="A58" s="223" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="224"/>
       <c r="C58" s="49"/>
       <c r="D58" s="205">
         <v>93772.25</v>
       </c>
       <c r="E58" s="150" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F58" s="50"/>
       <c r="G58" s="50"/>
       <c r="H58" s="50"/>
     </row>
     <row r="59" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="217" t="s">
-        <v>170</v>
-      </c>
-      <c r="B59" s="218"/>
+      <c r="A59" s="223" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" s="224"/>
       <c r="C59" s="33"/>
       <c r="D59" s="198">
         <v>331159.59999999998</v>
       </c>
       <c r="E59" s="150" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F59" s="39"/>
       <c r="G59" s="39"/>
@@ -3308,10 +3308,10 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="217" t="s">
+      <c r="A60" s="223" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="218"/>
+      <c r="B60" s="224"/>
       <c r="C60" s="33"/>
       <c r="D60" s="198"/>
       <c r="E60" s="164"/>
@@ -3330,8 +3330,8 @@
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="229"/>
-      <c r="B62" s="218"/>
+      <c r="A62" s="228"/>
+      <c r="B62" s="224"/>
       <c r="C62" s="25"/>
       <c r="D62" s="199"/>
       <c r="E62" s="48"/>
@@ -3386,11 +3386,11 @@
       <c r="Z63" s="4"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="230"/>
-      <c r="B64" s="231"/>
+      <c r="A64" s="229"/>
+      <c r="B64" s="230"/>
       <c r="C64" s="53"/>
-      <c r="D64" s="234"/>
-      <c r="E64" s="245"/>
+      <c r="D64" s="233"/>
+      <c r="E64" s="249"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -3414,11 +3414,11 @@
       <c r="Z64" s="4"/>
     </row>
     <row r="65" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="232"/>
-      <c r="B65" s="233"/>
+      <c r="A65" s="231"/>
+      <c r="B65" s="232"/>
       <c r="C65" s="53"/>
-      <c r="D65" s="235"/>
-      <c r="E65" s="235"/>
+      <c r="D65" s="234"/>
+      <c r="E65" s="234"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -3442,8 +3442,8 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="217"/>
-      <c r="B66" s="218"/>
+      <c r="A66" s="223"/>
+      <c r="B66" s="224"/>
       <c r="C66" s="25"/>
       <c r="D66" s="206"/>
       <c r="E66" s="54"/>
@@ -3470,8 +3470,8 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="217"/>
-      <c r="B67" s="218"/>
+      <c r="A67" s="223"/>
+      <c r="B67" s="224"/>
       <c r="C67" s="25"/>
       <c r="D67" s="206"/>
       <c r="E67" s="54"/>
@@ -3498,8 +3498,8 @@
       <c r="Z67" s="4"/>
     </row>
     <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="217"/>
-      <c r="B68" s="218"/>
+      <c r="A68" s="223"/>
+      <c r="B68" s="224"/>
       <c r="C68" s="25"/>
       <c r="D68" s="206"/>
       <c r="E68" s="48"/>
@@ -3533,8 +3533,8 @@
       <c r="Z69" s="4"/>
     </row>
     <row r="70" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="217"/>
-      <c r="B70" s="218"/>
+      <c r="A70" s="223"/>
+      <c r="B70" s="224"/>
       <c r="C70" s="25"/>
       <c r="D70" s="206"/>
       <c r="E70" s="48"/>
@@ -3589,8 +3589,8 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="217"/>
-      <c r="B72" s="218"/>
+      <c r="A72" s="223"/>
+      <c r="B72" s="224"/>
       <c r="C72" s="25"/>
       <c r="D72" s="206"/>
       <c r="E72" s="57"/>
@@ -3617,8 +3617,8 @@
       <c r="Z72" s="4"/>
     </row>
     <row r="73" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="217"/>
-      <c r="B73" s="218"/>
+      <c r="A73" s="223"/>
+      <c r="B73" s="224"/>
       <c r="C73" s="25"/>
       <c r="D73" s="206"/>
       <c r="E73" s="57"/>
@@ -3645,8 +3645,8 @@
       <c r="Z73" s="4"/>
     </row>
     <row r="74" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="225"/>
-      <c r="B74" s="218"/>
+      <c r="A74" s="251"/>
+      <c r="B74" s="224"/>
       <c r="C74" s="58"/>
       <c r="D74" s="206"/>
       <c r="E74" s="57"/>
@@ -3694,8 +3694,8 @@
       <c r="E76" s="59"/>
     </row>
     <row r="77" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="217"/>
-      <c r="B77" s="218"/>
+      <c r="A77" s="223"/>
+      <c r="B77" s="224"/>
       <c r="C77" s="60"/>
       <c r="D77" s="201"/>
       <c r="E77" s="57"/>
@@ -3722,15 +3722,15 @@
       <c r="Z77" s="4"/>
     </row>
     <row r="78" spans="1:26" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="217"/>
-      <c r="B78" s="228"/>
+      <c r="A78" s="223"/>
+      <c r="B78" s="227"/>
       <c r="C78" s="61"/>
       <c r="D78" s="201"/>
       <c r="E78" s="62"/>
     </row>
     <row r="79" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="225"/>
-      <c r="B79" s="218"/>
+      <c r="A79" s="251"/>
+      <c r="B79" s="224"/>
       <c r="C79" s="25"/>
       <c r="D79" s="201"/>
       <c r="E79" s="62"/>
@@ -3784,7 +3784,7 @@
     </row>
     <row r="83" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B83" s="65"/>
       <c r="C83" s="29"/>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B84" s="25"/>
       <c r="C84" s="25"/>
-      <c r="D84" s="265">
+      <c r="D84" s="222">
         <f>21359.46</f>
         <v>21359.46</v>
       </c>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="69" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B88" s="69"/>
       <c r="C88" s="69"/>
@@ -4382,20 +4382,20 @@
       <c r="E108" s="4"/>
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="266" t="s">
-        <v>181</v>
-      </c>
-      <c r="B109" s="266"/>
-      <c r="C109" s="266"/>
-      <c r="D109" s="266"/>
-      <c r="E109" s="266"/>
+      <c r="A109" s="252" t="s">
+        <v>180</v>
+      </c>
+      <c r="B109" s="252"/>
+      <c r="C109" s="252"/>
+      <c r="D109" s="252"/>
+      <c r="E109" s="252"/>
     </row>
     <row r="110" spans="1:26" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="266"/>
-      <c r="B110" s="266"/>
-      <c r="C110" s="266"/>
-      <c r="D110" s="266"/>
-      <c r="E110" s="266"/>
+      <c r="A110" s="252"/>
+      <c r="B110" s="252"/>
+      <c r="C110" s="252"/>
+      <c r="D110" s="252"/>
+      <c r="E110" s="252"/>
     </row>
     <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4"/>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="87" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B116" s="88">
         <f>B139</f>
@@ -4696,16 +4696,16 @@
     <row r="131" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="132" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="219" t="s">
+      <c r="A133" s="250" t="s">
         <v>43</v>
       </c>
-      <c r="B133" s="220"/>
-      <c r="C133" s="221"/>
+      <c r="B133" s="245"/>
+      <c r="C133" s="239"/>
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="222"/>
-      <c r="B134" s="223"/>
-      <c r="C134" s="224"/>
+      <c r="A134" s="242"/>
+      <c r="B134" s="247"/>
+      <c r="C134" s="243"/>
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="25"/>
@@ -5662,6 +5662,17 @@
     <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A133:C134"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A109:E110"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="B3:D4"/>
     <mergeCell ref="A78:B78"/>
@@ -5677,17 +5688,6 @@
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A133:C134"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A109:E110"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5796,74 +5796,74 @@
       <c r="B4" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="261" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="252" t="s">
+      <c r="D4" s="261" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="252" t="s">
+      <c r="E4" s="261" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="252" t="s">
+      <c r="F4" s="261" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="252" t="s">
+      <c r="G4" s="261" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="252" t="s">
+      <c r="H4" s="261" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="252" t="s">
+      <c r="I4" s="261" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="254" t="s">
+      <c r="J4" s="266" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="247" t="s">
+      <c r="K4" s="253" t="s">
         <v>123</v>
       </c>
-      <c r="L4" s="247" t="s">
+      <c r="L4" s="253" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="247" t="s">
+      <c r="M4" s="253" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="249" t="s">
+      <c r="N4" s="264" t="s">
         <v>58</v>
       </c>
       <c r="O4" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="P4" s="249" t="s">
+      <c r="P4" s="264" t="s">
         <v>60</v>
       </c>
-      <c r="Q4" s="247" t="s">
+      <c r="Q4" s="253" t="s">
         <v>61</v>
       </c>
       <c r="R4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="253"/>
-      <c r="B5" s="251"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="253"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="253"/>
-      <c r="G5" s="253"/>
-      <c r="H5" s="253"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="253"/>
-      <c r="M5" s="248"/>
-      <c r="N5" s="250"/>
+      <c r="A5" s="254"/>
+      <c r="B5" s="260"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="254"/>
+      <c r="M5" s="262"/>
+      <c r="N5" s="265"/>
       <c r="O5" s="110" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="253"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="254"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -6121,7 +6121,7 @@
         <v>78</v>
       </c>
       <c r="E10" s="214" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F10" s="215">
         <v>0.5</v>
@@ -6908,8 +6908,8 @@
         <v>0.17</v>
       </c>
       <c r="T22" s="174"/>
-      <c r="U22" s="261" t="s">
-        <v>179</v>
+      <c r="U22" s="218" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7813,95 +7813,95 @@
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="246" t="s">
-        <v>160</v>
-      </c>
-      <c r="E40" s="220"/>
-      <c r="F40" s="220"/>
-      <c r="G40" s="220"/>
-      <c r="H40" s="220"/>
-      <c r="I40" s="220"/>
-      <c r="J40" s="220"/>
-      <c r="K40" s="220"/>
-      <c r="L40" s="220"/>
-      <c r="M40" s="220"/>
-      <c r="N40" s="220"/>
-      <c r="O40" s="221"/>
+      <c r="D40" s="263" t="s">
+        <v>159</v>
+      </c>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="239"/>
       <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="240"/>
-      <c r="E41" s="243"/>
-      <c r="F41" s="243"/>
-      <c r="G41" s="243"/>
-      <c r="H41" s="243"/>
-      <c r="I41" s="243"/>
-      <c r="J41" s="243"/>
-      <c r="K41" s="243"/>
-      <c r="L41" s="243"/>
-      <c r="M41" s="243"/>
-      <c r="N41" s="243"/>
+      <c r="E41" s="246"/>
+      <c r="F41" s="246"/>
+      <c r="G41" s="246"/>
+      <c r="H41" s="246"/>
+      <c r="I41" s="246"/>
+      <c r="J41" s="246"/>
+      <c r="K41" s="246"/>
+      <c r="L41" s="246"/>
+      <c r="M41" s="246"/>
+      <c r="N41" s="246"/>
       <c r="O41" s="241"/>
       <c r="Q41" s="4"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="240"/>
-      <c r="E42" s="243"/>
-      <c r="F42" s="243"/>
-      <c r="G42" s="243"/>
-      <c r="H42" s="243"/>
-      <c r="I42" s="243"/>
-      <c r="J42" s="243"/>
-      <c r="K42" s="243"/>
-      <c r="L42" s="243"/>
-      <c r="M42" s="243"/>
-      <c r="N42" s="243"/>
+      <c r="E42" s="246"/>
+      <c r="F42" s="246"/>
+      <c r="G42" s="246"/>
+      <c r="H42" s="246"/>
+      <c r="I42" s="246"/>
+      <c r="J42" s="246"/>
+      <c r="K42" s="246"/>
+      <c r="L42" s="246"/>
+      <c r="M42" s="246"/>
+      <c r="N42" s="246"/>
       <c r="O42" s="241"/>
       <c r="Q42" s="4"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="240"/>
-      <c r="E43" s="243"/>
-      <c r="F43" s="243"/>
-      <c r="G43" s="243"/>
-      <c r="H43" s="243"/>
-      <c r="I43" s="243"/>
-      <c r="J43" s="243"/>
-      <c r="K43" s="243"/>
-      <c r="L43" s="243"/>
-      <c r="M43" s="243"/>
-      <c r="N43" s="243"/>
+      <c r="E43" s="246"/>
+      <c r="F43" s="246"/>
+      <c r="G43" s="246"/>
+      <c r="H43" s="246"/>
+      <c r="I43" s="246"/>
+      <c r="J43" s="246"/>
+      <c r="K43" s="246"/>
+      <c r="L43" s="246"/>
+      <c r="M43" s="246"/>
+      <c r="N43" s="246"/>
       <c r="O43" s="241"/>
       <c r="Q43" s="4"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="240"/>
-      <c r="E44" s="243"/>
-      <c r="F44" s="243"/>
-      <c r="G44" s="243"/>
-      <c r="H44" s="243"/>
-      <c r="I44" s="243"/>
-      <c r="J44" s="243"/>
-      <c r="K44" s="243"/>
-      <c r="L44" s="243"/>
-      <c r="M44" s="243"/>
-      <c r="N44" s="243"/>
+      <c r="E44" s="246"/>
+      <c r="F44" s="246"/>
+      <c r="G44" s="246"/>
+      <c r="H44" s="246"/>
+      <c r="I44" s="246"/>
+      <c r="J44" s="246"/>
+      <c r="K44" s="246"/>
+      <c r="L44" s="246"/>
+      <c r="M44" s="246"/>
+      <c r="N44" s="246"/>
       <c r="O44" s="241"/>
       <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="222"/>
-      <c r="E45" s="223"/>
-      <c r="F45" s="223"/>
-      <c r="G45" s="223"/>
-      <c r="H45" s="223"/>
-      <c r="I45" s="223"/>
-      <c r="J45" s="223"/>
-      <c r="K45" s="223"/>
-      <c r="L45" s="223"/>
-      <c r="M45" s="223"/>
-      <c r="N45" s="223"/>
-      <c r="O45" s="224"/>
+      <c r="D45" s="242"/>
+      <c r="E45" s="247"/>
+      <c r="F45" s="247"/>
+      <c r="G45" s="247"/>
+      <c r="H45" s="247"/>
+      <c r="I45" s="247"/>
+      <c r="J45" s="247"/>
+      <c r="K45" s="247"/>
+      <c r="L45" s="247"/>
+      <c r="M45" s="247"/>
+      <c r="N45" s="247"/>
+      <c r="O45" s="243"/>
       <c r="Q45" s="4"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13372,6 +13372,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D40:O45"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="F1:O1"/>
     <mergeCell ref="A4:A5"/>
@@ -13381,15 +13390,6 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="D40:O45"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/ILLIA/Mayo/ILLIA-MAYO.xlsx
+++ b/ILLIA/Mayo/ILLIA-MAYO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9ED015-2164-43C3-8F4E-532732E22653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7096294-C005-4DF3-B74E-89D4F4EFD27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="183">
   <si>
     <t>TELEFONO: 11 5320-2676</t>
   </si>
@@ -593,6 +593,9 @@
   </si>
   <si>
     <t xml:space="preserve">Debito </t>
+  </si>
+  <si>
+    <t>PABLO MAOYANO PAGO EL 31/05 PERO LA HABIAMOS CERRADO ANTES</t>
   </si>
 </sst>
 </file>
@@ -1573,7 +1576,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="268">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1903,10 +1906,24 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1937,36 +1954,37 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1978,21 +1996,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2291,11 +2295,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="225" t="s">
+      <c r="B3" s="233" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="225"/>
-      <c r="D3" s="225"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="233"/>
       <c r="E3" s="9"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -2303,9 +2307,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
-      <c r="B4" s="226"/>
-      <c r="C4" s="226"/>
-      <c r="D4" s="226"/>
+      <c r="B4" s="234"/>
+      <c r="C4" s="234"/>
+      <c r="D4" s="234"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -2343,13 +2347,13 @@
       <c r="I6" s="156"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="235" t="s">
+      <c r="A7" s="243" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="236"/>
-      <c r="E7" s="237"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="244"/>
+      <c r="D7" s="244"/>
+      <c r="E7" s="245"/>
       <c r="F7" s="17"/>
       <c r="G7" s="157"/>
       <c r="H7" s="157"/>
@@ -2362,10 +2366,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="238" t="s">
+      <c r="B9" s="246" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="239"/>
+      <c r="C9" s="225"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -2374,8 +2378,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="240"/>
-      <c r="C10" s="241"/>
+      <c r="B10" s="247"/>
+      <c r="C10" s="248"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -2384,8 +2388,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="242"/>
-      <c r="C11" s="243"/>
+      <c r="B11" s="226"/>
+      <c r="C11" s="228"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -2403,43 +2407,43 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="244" t="s">
+      <c r="A14" s="249" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="245"/>
-      <c r="C14" s="245"/>
-      <c r="D14" s="245"/>
-      <c r="E14" s="239"/>
+      <c r="B14" s="224"/>
+      <c r="C14" s="224"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="225"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="240"/>
-      <c r="B15" s="246"/>
-      <c r="C15" s="246"/>
-      <c r="D15" s="246"/>
-      <c r="E15" s="241"/>
+      <c r="A15" s="247"/>
+      <c r="B15" s="250"/>
+      <c r="C15" s="250"/>
+      <c r="D15" s="250"/>
+      <c r="E15" s="248"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="240"/>
-      <c r="B16" s="246"/>
-      <c r="C16" s="246"/>
-      <c r="D16" s="246"/>
-      <c r="E16" s="241"/>
+      <c r="A16" s="247"/>
+      <c r="B16" s="250"/>
+      <c r="C16" s="250"/>
+      <c r="D16" s="250"/>
+      <c r="E16" s="248"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="242"/>
-      <c r="B17" s="247"/>
-      <c r="C17" s="247"/>
-      <c r="D17" s="247"/>
-      <c r="E17" s="243"/>
+      <c r="A17" s="226"/>
+      <c r="B17" s="227"/>
+      <c r="C17" s="227"/>
+      <c r="D17" s="227"/>
+      <c r="E17" s="228"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
@@ -2962,10 +2966,10 @@
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="248" t="s">
+      <c r="A44" s="251" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="224"/>
+      <c r="B44" s="230"/>
       <c r="C44" s="37"/>
       <c r="D44" s="199">
         <v>50274.73</v>
@@ -3162,10 +3166,10 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="228" t="s">
+      <c r="A54" s="236" t="s">
         <v>167</v>
       </c>
-      <c r="B54" s="224"/>
+      <c r="B54" s="230"/>
       <c r="C54" s="25"/>
       <c r="D54" s="203">
         <v>94000</v>
@@ -3246,10 +3250,10 @@
       <c r="H56" s="50"/>
     </row>
     <row r="57" spans="1:26" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="223" t="s">
+      <c r="A57" s="229" t="s">
         <v>177</v>
       </c>
-      <c r="B57" s="224"/>
+      <c r="B57" s="230"/>
       <c r="C57" s="49"/>
       <c r="D57" s="204"/>
       <c r="E57" s="150"/>
@@ -3258,10 +3262,10 @@
       <c r="H57" s="50"/>
     </row>
     <row r="58" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="223" t="s">
+      <c r="A58" s="229" t="s">
         <v>168</v>
       </c>
-      <c r="B58" s="224"/>
+      <c r="B58" s="230"/>
       <c r="C58" s="49"/>
       <c r="D58" s="205">
         <v>93772.25</v>
@@ -3274,10 +3278,10 @@
       <c r="H58" s="50"/>
     </row>
     <row r="59" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="223" t="s">
+      <c r="A59" s="229" t="s">
         <v>169</v>
       </c>
-      <c r="B59" s="224"/>
+      <c r="B59" s="230"/>
       <c r="C59" s="33"/>
       <c r="D59" s="198">
         <v>331159.59999999998</v>
@@ -3308,10 +3312,10 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="223" t="s">
+      <c r="A60" s="229" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="224"/>
+      <c r="B60" s="230"/>
       <c r="C60" s="33"/>
       <c r="D60" s="198"/>
       <c r="E60" s="164"/>
@@ -3330,8 +3334,8 @@
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="228"/>
-      <c r="B62" s="224"/>
+      <c r="A62" s="236"/>
+      <c r="B62" s="230"/>
       <c r="C62" s="25"/>
       <c r="D62" s="199"/>
       <c r="E62" s="48"/>
@@ -3386,11 +3390,11 @@
       <c r="Z63" s="4"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="229"/>
-      <c r="B64" s="230"/>
+      <c r="A64" s="237"/>
+      <c r="B64" s="238"/>
       <c r="C64" s="53"/>
-      <c r="D64" s="233"/>
-      <c r="E64" s="249"/>
+      <c r="D64" s="241"/>
+      <c r="E64" s="252"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -3414,11 +3418,11 @@
       <c r="Z64" s="4"/>
     </row>
     <row r="65" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="231"/>
-      <c r="B65" s="232"/>
+      <c r="A65" s="239"/>
+      <c r="B65" s="240"/>
       <c r="C65" s="53"/>
-      <c r="D65" s="234"/>
-      <c r="E65" s="234"/>
+      <c r="D65" s="242"/>
+      <c r="E65" s="242"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -3442,8 +3446,8 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="223"/>
-      <c r="B66" s="224"/>
+      <c r="A66" s="229"/>
+      <c r="B66" s="230"/>
       <c r="C66" s="25"/>
       <c r="D66" s="206"/>
       <c r="E66" s="54"/>
@@ -3470,8 +3474,8 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="223"/>
-      <c r="B67" s="224"/>
+      <c r="A67" s="229"/>
+      <c r="B67" s="230"/>
       <c r="C67" s="25"/>
       <c r="D67" s="206"/>
       <c r="E67" s="54"/>
@@ -3498,8 +3502,8 @@
       <c r="Z67" s="4"/>
     </row>
     <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="223"/>
-      <c r="B68" s="224"/>
+      <c r="A68" s="229"/>
+      <c r="B68" s="230"/>
       <c r="C68" s="25"/>
       <c r="D68" s="206"/>
       <c r="E68" s="48"/>
@@ -3533,8 +3537,8 @@
       <c r="Z69" s="4"/>
     </row>
     <row r="70" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="223"/>
-      <c r="B70" s="224"/>
+      <c r="A70" s="229"/>
+      <c r="B70" s="230"/>
       <c r="C70" s="25"/>
       <c r="D70" s="206"/>
       <c r="E70" s="48"/>
@@ -3589,8 +3593,8 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="223"/>
-      <c r="B72" s="224"/>
+      <c r="A72" s="229"/>
+      <c r="B72" s="230"/>
       <c r="C72" s="25"/>
       <c r="D72" s="206"/>
       <c r="E72" s="57"/>
@@ -3617,8 +3621,8 @@
       <c r="Z72" s="4"/>
     </row>
     <row r="73" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="223"/>
-      <c r="B73" s="224"/>
+      <c r="A73" s="229"/>
+      <c r="B73" s="230"/>
       <c r="C73" s="25"/>
       <c r="D73" s="206"/>
       <c r="E73" s="57"/>
@@ -3645,8 +3649,8 @@
       <c r="Z73" s="4"/>
     </row>
     <row r="74" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="251"/>
-      <c r="B74" s="224"/>
+      <c r="A74" s="231"/>
+      <c r="B74" s="230"/>
       <c r="C74" s="58"/>
       <c r="D74" s="206"/>
       <c r="E74" s="57"/>
@@ -3694,8 +3698,8 @@
       <c r="E76" s="59"/>
     </row>
     <row r="77" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="223"/>
-      <c r="B77" s="224"/>
+      <c r="A77" s="229"/>
+      <c r="B77" s="230"/>
       <c r="C77" s="60"/>
       <c r="D77" s="201"/>
       <c r="E77" s="57"/>
@@ -3722,15 +3726,15 @@
       <c r="Z77" s="4"/>
     </row>
     <row r="78" spans="1:26" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="223"/>
-      <c r="B78" s="227"/>
+      <c r="A78" s="229"/>
+      <c r="B78" s="235"/>
       <c r="C78" s="61"/>
       <c r="D78" s="201"/>
       <c r="E78" s="62"/>
     </row>
     <row r="79" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="251"/>
-      <c r="B79" s="224"/>
+      <c r="A79" s="231"/>
+      <c r="B79" s="230"/>
       <c r="C79" s="25"/>
       <c r="D79" s="201"/>
       <c r="E79" s="62"/>
@@ -4382,20 +4386,20 @@
       <c r="E108" s="4"/>
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="252" t="s">
+      <c r="A109" s="232" t="s">
         <v>180</v>
       </c>
-      <c r="B109" s="252"/>
-      <c r="C109" s="252"/>
-      <c r="D109" s="252"/>
-      <c r="E109" s="252"/>
+      <c r="B109" s="232"/>
+      <c r="C109" s="232"/>
+      <c r="D109" s="232"/>
+      <c r="E109" s="232"/>
     </row>
     <row r="110" spans="1:26" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="252"/>
-      <c r="B110" s="252"/>
-      <c r="C110" s="252"/>
-      <c r="D110" s="252"/>
-      <c r="E110" s="252"/>
+      <c r="A110" s="232"/>
+      <c r="B110" s="232"/>
+      <c r="C110" s="232"/>
+      <c r="D110" s="232"/>
+      <c r="E110" s="232"/>
     </row>
     <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4"/>
@@ -4696,16 +4700,16 @@
     <row r="131" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="132" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="250" t="s">
+      <c r="A133" s="223" t="s">
         <v>43</v>
       </c>
-      <c r="B133" s="245"/>
-      <c r="C133" s="239"/>
+      <c r="B133" s="224"/>
+      <c r="C133" s="225"/>
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="242"/>
-      <c r="B134" s="247"/>
-      <c r="C134" s="243"/>
+      <c r="A134" s="226"/>
+      <c r="B134" s="227"/>
+      <c r="C134" s="228"/>
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="25"/>
@@ -5662,17 +5666,6 @@
     <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A133:C134"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A109:E110"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="B3:D4"/>
     <mergeCell ref="A78:B78"/>
@@ -5688,6 +5681,17 @@
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A133:C134"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A109:E110"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5728,16 +5732,16 @@
       <c r="C1" s="104"/>
       <c r="D1" s="104"/>
       <c r="E1" s="104"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="256"/>
-      <c r="H1" s="256"/>
-      <c r="I1" s="256"/>
-      <c r="J1" s="256"/>
-      <c r="K1" s="256"/>
-      <c r="L1" s="256"/>
-      <c r="M1" s="256"/>
-      <c r="N1" s="256"/>
-      <c r="O1" s="257"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="263"/>
+      <c r="H1" s="263"/>
+      <c r="I1" s="263"/>
+      <c r="J1" s="263"/>
+      <c r="K1" s="263"/>
+      <c r="L1" s="263"/>
+      <c r="M1" s="263"/>
+      <c r="N1" s="263"/>
+      <c r="O1" s="264"/>
       <c r="P1" s="104"/>
       <c r="Q1" s="104"/>
     </row>
@@ -5790,80 +5794,80 @@
       <c r="Q3" s="108"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="258" t="s">
+      <c r="A4" s="265" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="266" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="261" t="s">
+      <c r="C4" s="259" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="261" t="s">
+      <c r="D4" s="259" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="261" t="s">
+      <c r="E4" s="259" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="261" t="s">
+      <c r="F4" s="259" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="261" t="s">
+      <c r="G4" s="259" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="261" t="s">
+      <c r="H4" s="259" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="261" t="s">
+      <c r="I4" s="259" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="266" t="s">
+      <c r="J4" s="261" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="253" t="s">
+      <c r="K4" s="254" t="s">
         <v>123</v>
       </c>
-      <c r="L4" s="253" t="s">
+      <c r="L4" s="254" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="253" t="s">
+      <c r="M4" s="254" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="264" t="s">
+      <c r="N4" s="256" t="s">
         <v>58</v>
       </c>
       <c r="O4" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="P4" s="264" t="s">
+      <c r="P4" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="Q4" s="253" t="s">
+      <c r="Q4" s="254" t="s">
         <v>61</v>
       </c>
       <c r="R4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="254"/>
-      <c r="B5" s="260"/>
-      <c r="C5" s="254"/>
-      <c r="D5" s="254"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="254"/>
-      <c r="G5" s="254"/>
-      <c r="H5" s="254"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="254"/>
-      <c r="M5" s="262"/>
-      <c r="N5" s="265"/>
+      <c r="A5" s="260"/>
+      <c r="B5" s="258"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="260"/>
+      <c r="M5" s="255"/>
+      <c r="N5" s="257"/>
       <c r="O5" s="110" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="254"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="260"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -7226,7 +7230,9 @@
         <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
-      <c r="T27" s="174"/>
+      <c r="T27" s="267" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="28" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
@@ -7813,95 +7819,95 @@
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="263" t="s">
+      <c r="D40" s="253" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="245"/>
-      <c r="F40" s="245"/>
-      <c r="G40" s="245"/>
-      <c r="H40" s="245"/>
-      <c r="I40" s="245"/>
-      <c r="J40" s="245"/>
-      <c r="K40" s="245"/>
-      <c r="L40" s="245"/>
-      <c r="M40" s="245"/>
-      <c r="N40" s="245"/>
-      <c r="O40" s="239"/>
+      <c r="E40" s="224"/>
+      <c r="F40" s="224"/>
+      <c r="G40" s="224"/>
+      <c r="H40" s="224"/>
+      <c r="I40" s="224"/>
+      <c r="J40" s="224"/>
+      <c r="K40" s="224"/>
+      <c r="L40" s="224"/>
+      <c r="M40" s="224"/>
+      <c r="N40" s="224"/>
+      <c r="O40" s="225"/>
       <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="240"/>
-      <c r="E41" s="246"/>
-      <c r="F41" s="246"/>
-      <c r="G41" s="246"/>
-      <c r="H41" s="246"/>
-      <c r="I41" s="246"/>
-      <c r="J41" s="246"/>
-      <c r="K41" s="246"/>
-      <c r="L41" s="246"/>
-      <c r="M41" s="246"/>
-      <c r="N41" s="246"/>
-      <c r="O41" s="241"/>
+      <c r="D41" s="247"/>
+      <c r="E41" s="250"/>
+      <c r="F41" s="250"/>
+      <c r="G41" s="250"/>
+      <c r="H41" s="250"/>
+      <c r="I41" s="250"/>
+      <c r="J41" s="250"/>
+      <c r="K41" s="250"/>
+      <c r="L41" s="250"/>
+      <c r="M41" s="250"/>
+      <c r="N41" s="250"/>
+      <c r="O41" s="248"/>
       <c r="Q41" s="4"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="240"/>
-      <c r="E42" s="246"/>
-      <c r="F42" s="246"/>
-      <c r="G42" s="246"/>
-      <c r="H42" s="246"/>
-      <c r="I42" s="246"/>
-      <c r="J42" s="246"/>
-      <c r="K42" s="246"/>
-      <c r="L42" s="246"/>
-      <c r="M42" s="246"/>
-      <c r="N42" s="246"/>
-      <c r="O42" s="241"/>
+      <c r="D42" s="247"/>
+      <c r="E42" s="250"/>
+      <c r="F42" s="250"/>
+      <c r="G42" s="250"/>
+      <c r="H42" s="250"/>
+      <c r="I42" s="250"/>
+      <c r="J42" s="250"/>
+      <c r="K42" s="250"/>
+      <c r="L42" s="250"/>
+      <c r="M42" s="250"/>
+      <c r="N42" s="250"/>
+      <c r="O42" s="248"/>
       <c r="Q42" s="4"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="240"/>
-      <c r="E43" s="246"/>
-      <c r="F43" s="246"/>
-      <c r="G43" s="246"/>
-      <c r="H43" s="246"/>
-      <c r="I43" s="246"/>
-      <c r="J43" s="246"/>
-      <c r="K43" s="246"/>
-      <c r="L43" s="246"/>
-      <c r="M43" s="246"/>
-      <c r="N43" s="246"/>
-      <c r="O43" s="241"/>
+      <c r="D43" s="247"/>
+      <c r="E43" s="250"/>
+      <c r="F43" s="250"/>
+      <c r="G43" s="250"/>
+      <c r="H43" s="250"/>
+      <c r="I43" s="250"/>
+      <c r="J43" s="250"/>
+      <c r="K43" s="250"/>
+      <c r="L43" s="250"/>
+      <c r="M43" s="250"/>
+      <c r="N43" s="250"/>
+      <c r="O43" s="248"/>
       <c r="Q43" s="4"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="240"/>
-      <c r="E44" s="246"/>
-      <c r="F44" s="246"/>
-      <c r="G44" s="246"/>
-      <c r="H44" s="246"/>
-      <c r="I44" s="246"/>
-      <c r="J44" s="246"/>
-      <c r="K44" s="246"/>
-      <c r="L44" s="246"/>
-      <c r="M44" s="246"/>
-      <c r="N44" s="246"/>
-      <c r="O44" s="241"/>
+      <c r="D44" s="247"/>
+      <c r="E44" s="250"/>
+      <c r="F44" s="250"/>
+      <c r="G44" s="250"/>
+      <c r="H44" s="250"/>
+      <c r="I44" s="250"/>
+      <c r="J44" s="250"/>
+      <c r="K44" s="250"/>
+      <c r="L44" s="250"/>
+      <c r="M44" s="250"/>
+      <c r="N44" s="250"/>
+      <c r="O44" s="248"/>
       <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="242"/>
-      <c r="E45" s="247"/>
-      <c r="F45" s="247"/>
-      <c r="G45" s="247"/>
-      <c r="H45" s="247"/>
-      <c r="I45" s="247"/>
-      <c r="J45" s="247"/>
-      <c r="K45" s="247"/>
-      <c r="L45" s="247"/>
-      <c r="M45" s="247"/>
-      <c r="N45" s="247"/>
-      <c r="O45" s="243"/>
+      <c r="D45" s="226"/>
+      <c r="E45" s="227"/>
+      <c r="F45" s="227"/>
+      <c r="G45" s="227"/>
+      <c r="H45" s="227"/>
+      <c r="I45" s="227"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="227"/>
+      <c r="L45" s="227"/>
+      <c r="M45" s="227"/>
+      <c r="N45" s="227"/>
+      <c r="O45" s="228"/>
       <c r="Q45" s="4"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13372,6 +13378,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
@@ -13381,15 +13396,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
